--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/9802-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/9802-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F7D2DBD-8CA7-455A-B269-07DED6758BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A88D6EA4-4DE1-4B8C-B8DD-42F4B881E860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{4EDA53CA-4044-4D58-B551-E8640F7F9691}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{372A820A-FF5E-4D21-BFB5-36374411480B}"/>
   </bookViews>
   <sheets>
     <sheet name="9802-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1487,25 +1487,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C73B6535-7394-4DF1-A7E1-C484E59CA88E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8D56C3C-BAF6-4515-8233-86C43E712121}">
   <dimension ref="A1:R32"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1533,7 +1533,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1563,7 +1563,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1659,7 +1659,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2026</v>
       </c>
@@ -1713,7 +1713,7 @@
         <v>5.41</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>3.29</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1825,7 +1825,7 @@
         <v>2.12</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2025</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>4.34</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1935,7 +1935,7 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1991,7 +1991,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2024</v>
       </c>
@@ -2045,7 +2045,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>2.56</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v>1.61</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="39">
         <v>2023</v>
       </c>
@@ -2211,7 +2211,7 @@
         <v>5.22</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>25</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="37">
         <v>2022</v>
       </c>
@@ -2377,7 +2377,7 @@
         <v>2.59</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2433,7 +2433,7 @@
         <v>1.46</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2021</v>
       </c>
@@ -2543,7 +2543,7 @@
         <v>3.55</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2599,7 +2599,7 @@
         <v>1.71</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2655,7 +2655,7 @@
         <v>1.83</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="37">
         <v>2020</v>
       </c>
@@ -2709,7 +2709,7 @@
         <v>5.18</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="39">
         <v>2019</v>
       </c>
@@ -2763,7 +2763,7 @@
         <v>4.8600000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2018</v>
       </c>
@@ -2817,7 +2817,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="39">
         <v>2017</v>
       </c>
@@ -2871,7 +2871,7 @@
         <v>3.64</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="37">
         <v>2016</v>
       </c>
@@ -2925,7 +2925,7 @@
         <v>3.15</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="39">
         <v>2015</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="37">
         <v>2014</v>
       </c>
@@ -3033,7 +3033,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2013</v>
       </c>
@@ -3087,7 +3087,7 @@
         <v>5.82</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="37">
         <v>2012</v>
       </c>
@@ -3141,7 +3141,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="39" t="s">
         <v>48</v>
       </c>
